--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
         <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>5.1</v>
+        <v>3.79</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
         <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>2.49</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.49</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.49</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
         <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>5.1</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.49</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>1.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>3.79</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>3.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>2.49</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>8.949999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>3.22</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O8" t="n">
         <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>3.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>3.22</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>3.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>2.49</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>3.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.49</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>8.949999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1052,40 +1052,40 @@
         <v>4.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
         <v>1.8</v>
@@ -1094,13 +1094,13 @@
         <v>1.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>3.22</v>
+        <v>3.79</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>3.22</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>8.949999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>2.49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>5.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O7" t="n">
         <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>5.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>8.949999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>3.22</v>
+        <v>3.79</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>8.949999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.49</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>3.22</v>
+        <v>3.79</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.79</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>8.949999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
         <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>8.949999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>5.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>3.22</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.49</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>3.79</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>3.22</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>2.49</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>8.949999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,55 +2324,55 @@
         <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,34 +3278,34 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
         <v>1.73</v>
@@ -3314,19 +3314,19 @@
         <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3437,55 +3437,55 @@
         <v>3.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3.79</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>8.949999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="R8" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.2</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.59</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
         <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.06</v>
@@ -929,7 +929,7 @@
         <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
         <v>1.25</v>
@@ -938,7 +938,7 @@
         <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
         <v>1.91</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
         <v>1.62</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S6" t="n">
         <v>1.27</v>
       </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.32</v>
-      </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
         <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="U8" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.49</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>3.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.22</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
         <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>5.1</v>
+        <v>3.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.38</v>
       </c>
-      <c r="O16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="U17" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AG17" t="n">
         <v>1.95</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
         <v>1.44</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>5.1</v>
+        <v>3.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.2</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.59</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.49</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
         <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,37 +1997,37 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>8.949999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>3.34</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.22</v>
@@ -2036,25 +2036,25 @@
         <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
         <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="U11" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -734,22 +734,22 @@
         <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T2" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.82</v>
+        <v>3.07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -758,19 +758,19 @@
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="AD2" t="n">
         <v>1.25</v>
@@ -779,10 +779,10 @@
         <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.66</v>
+        <v>3.13</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>4.69</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4.74</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
         <v>1.91</v>
@@ -1064,7 +1064,7 @@
         <v>4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.85</v>
@@ -1079,7 +1079,7 @@
         <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.33</v>
@@ -1088,10 +1088,10 @@
         <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="n">
         <v>1.36</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
         <v>2.25</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>3.22</v>
+        <v>3.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="R7" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>8.949999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="U10" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
         <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.49</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
         <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
         <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>3.22</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.16</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>5.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>3.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,37 +2156,37 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>8.949999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>3.34</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.22</v>
@@ -2195,25 +2195,25 @@
         <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
         <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.38</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P17" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
         <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="R8" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>8.949999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>3.22</v>
+        <v>5.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.16</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="U11" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
         <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>3.95</v>
+        <v>4.29</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.38</v>
       </c>
-      <c r="O16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="U17" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AG17" t="n">
         <v>1.95</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
         <v>1.44</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="U6" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>8.949999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,37 +1679,37 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.34</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.22</v>
@@ -1718,26 +1718,26 @@
         <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG8" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3.79</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>3.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,61 +2951,61 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="U16" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AG16" t="n">
         <v>1.95</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
         <v>1.44</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S18" t="n">
         <v>1.38</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P18" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -728,10 +728,10 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -893,22 +893,22 @@
         <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
         <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -917,16 +917,16 @@
         <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
         <v>3.69</v>
@@ -941,7 +941,7 @@
         <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.91</v>
@@ -1061,13 +1061,13 @@
         <v>1.16</v>
       </c>
       <c r="T4" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
         <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="W4" t="n">
         <v>1.22</v>
@@ -1076,10 +1076,10 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA4" t="n">
         <v>1.33</v>
@@ -1088,13 +1088,13 @@
         <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF4" t="n">
         <v>1.4</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
         <v>2.25</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="R5" t="n">
         <v>2.21</v>
@@ -1223,13 +1223,13 @@
         <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1247,19 +1247,19 @@
         <v>2.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
         <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>3.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="P7" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>2.49</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>8.949999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA8" t="n">
         <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
         <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>3.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="R10" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.22</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2483,55 +2483,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="P15" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="U18" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
         <v>1.95</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK18" t="n">
         <v>1.44</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
         <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S19" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
         <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1520,58 +1520,58 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="P7" t="n">
-        <v>5.1</v>
+        <v>4.69</v>
       </c>
       <c r="Q7" t="n">
         <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
         <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF7" t="n">
         <v>1.61</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
         <v>2.25</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.49</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>7.5</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.9</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.43</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>3.79</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>3.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,37 +2156,37 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>2.53</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>8.949999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>3.18</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.22</v>
@@ -2195,25 +2195,25 @@
         <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,37 +2315,37 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.48</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.25</v>
@@ -2357,22 +2357,22 @@
         <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
         <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2483,55 +2483,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.2</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AD18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.1</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
         <v>1.95</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
         <v>1.44</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S6" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="T6" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.12</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.69</v>
+        <v>3.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T9" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.83</v>
+        <v>2.39</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.81</v>
+        <v>4.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.15</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>4.15</v>
+        <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>4.69</v>
+        <v>2.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
         <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T10" t="n">
         <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AC10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>4.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
         <v>2.15</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.95</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.36</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG17" t="n">
         <v>1.95</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK17" t="n">
         <v>1.44</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P2" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -893,71 +893,71 @@
         <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
         <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
         <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.13</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
         <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>3.81</v>
+        <v>2.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.95</v>
+        <v>3.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>4.69</v>
+        <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2483,55 +2483,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="O15" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC15" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
         <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>1.91</v>
@@ -1058,16 +1058,16 @@
         <v>2.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
         <v>1.22</v>
@@ -1076,25 +1076,25 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
         <v>1.4</v>
@@ -1116,7 +1116,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
         <v>1.29</v>
@@ -1223,13 +1223,13 @@
         <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1241,10 +1241,10 @@
         <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
         <v>2.52</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="P6" t="n">
-        <v>4.69</v>
+        <v>8.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
         <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
         <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.16</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.45</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.81</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>7.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.77</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P12" t="n">
         <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="R12" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
         <v>3.02</v>
       </c>
       <c r="U12" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AC12" t="n">
         <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2483,13 +2483,13 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.25</v>
+        <v>4.13</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
         <v>2.7</v>
@@ -2498,7 +2498,7 @@
         <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
@@ -2507,19 +2507,19 @@
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.77</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q19" t="n">
         <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.04</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE19" t="n">
         <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="P6" t="n">
-        <v>8.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.74</v>
+        <v>4.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="P9" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,34 +1997,34 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
@@ -2033,28 +2033,28 @@
         <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
         <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>8.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
         <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2483,55 +2483,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>4.13</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,10 +2801,10 @@
         <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="R15" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="S15" t="n">
         <v>1.44</v>
@@ -2846,10 +2846,10 @@
         <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
         <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>8.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.02</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AD8" t="n">
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.43</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>4.8</v>
+        <v>3.07</v>
       </c>
       <c r="P11" t="n">
-        <v>8.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2483,55 +2483,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.13</v>
+        <v>2.35</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
         <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="R15" t="n">
         <v>1.97</v>
@@ -2825,10 +2825,10 @@
         <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
         <v>2.25</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
         <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
         <v>3.25</v>
@@ -3476,16 +3476,16 @@
         <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
         <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.95</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.25</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z6" t="n">
-        <v>4.92</v>
+        <v>3.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,34 +1520,34 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
@@ -1556,28 +1556,28 @@
         <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AF7" t="n">
         <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>8.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.74</v>
+        <v>4.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>8.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
         <v>3.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="O10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P10" t="n">
         <v>3.8</v>
       </c>
-      <c r="P10" t="n">
-        <v>4.4</v>
-      </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.95</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2483,55 +2483,55 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.13</v>
+        <v>2.35</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.05</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2642,55 +2642,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.35</v>
+        <v>4.13</v>
       </c>
       <c r="R14" t="n">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -920,28 +920,28 @@
         <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AA3" t="n">
         <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
         <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
         <v>1.91</v>
@@ -1058,19 +1058,19 @@
         <v>2.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T4" t="n">
         <v>4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1082,19 +1082,19 @@
         <v>7.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
         <v>1.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF4" t="n">
         <v>1.4</v>
@@ -1116,7 +1116,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>3.46</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
         <v>2.7</v>
@@ -1256,7 +1256,7 @@
         <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
         <v>2.34</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>8.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.28</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.59</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
         <v>3.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="O8" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.5</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.25</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.09</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>8.75</v>
+        <v>4.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,25 +2315,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>3.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.9</v>
+        <v>4.61</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S12" t="n">
         <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
         <v>2.45</v>
@@ -2345,10 +2345,10 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
         <v>3.54</v>
@@ -2357,16 +2357,16 @@
         <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
         <v>1.92</v>
@@ -2492,7 +2492,7 @@
         <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
         <v>3.42</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
         <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R15" t="n">
         <v>1.97</v>
@@ -2819,7 +2819,7 @@
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.08</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,37 +2951,37 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
         <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.15</v>
@@ -2990,25 +2990,25 @@
         <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,28 +3428,28 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
         <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.28</v>
@@ -3461,16 +3461,16 @@
         <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC19" t="n">
         <v>4.8</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK19" t="n">
         <v>1.43</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1253,7 +1253,7 @@
         <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
         <v>1.5</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="O6" t="n">
-        <v>4.8</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>8.75</v>
+        <v>3.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.53</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>4.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>4.55</v>
+        <v>2.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.87</v>
+        <v>8.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>3.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>2.53</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P11" t="n">
-        <v>3.83</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
         <v>3.42</v>
@@ -2501,28 +2501,28 @@
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
         <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
@@ -2792,19 +2792,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
         <v>1.44</v>
@@ -2813,10 +2813,10 @@
         <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
@@ -2828,13 +2828,13 @@
         <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>4.2</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.86</v>
+        <v>2.53</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
-        <v>3.83</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>2.41</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.55</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>3.02</v>
       </c>
       <c r="R7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.5</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
         <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>3.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>4.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.3</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.53</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>3.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S19" t="n">
         <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U19" t="n">
         <v>3.4</v>
@@ -3458,7 +3458,7 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
         <v>1.52</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AC2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>1.86</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>3.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.41</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>8.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.02</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>2.41</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.55</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.02</v>
       </c>
       <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.3</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>3.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.08</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P9" t="n">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>8.75</v>
+        <v>4.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>3.83</v>
+        <v>2.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -725,43 +725,43 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>3.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.8</v>
@@ -770,19 +770,19 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
         <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.03</v>
@@ -917,31 +917,31 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
         <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>4.1</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>2.75</v>
@@ -1064,13 +1064,13 @@
         <v>4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1079,28 +1079,28 @@
         <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
         <v>1.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
         <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
         <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="R5" t="n">
         <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
         <v>3.25</v>
@@ -1247,19 +1247,19 @@
         <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
         <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
         <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK5" t="n">
         <v>1.57</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.86</v>
+        <v>2.53</v>
       </c>
       <c r="O6" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>8.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,22 +1679,22 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
         <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
         <v>2.96</v>
@@ -1715,28 +1715,28 @@
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD8" t="n">
         <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
         <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P10" t="n">
         <v>3.8</v>
       </c>
-      <c r="P10" t="n">
-        <v>4.55</v>
-      </c>
       <c r="Q10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.95</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.25</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.34</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
         <v>1.55</v>
@@ -2330,22 +2330,22 @@
         <v>2.42</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.22</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>4.13</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="S13" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.17</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="V14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.33</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>2.5</v>
@@ -2807,7 +2807,7 @@
         <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
         <v>2.54</v>
@@ -2822,28 +2822,28 @@
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
         <v>1.95</v>
@@ -2865,7 +2865,7 @@
         <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
         <v>3.28</v>
@@ -3464,13 +3464,13 @@
         <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AA19" t="n">
         <v>2.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>4.8</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="n">
         <v>3.8</v>
       </c>
-      <c r="P7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="Q7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.95</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,34 +1679,34 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.49</v>
+        <v>8.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1715,28 +1715,28 @@
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
         <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P9" t="n">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="AA10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.15</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>8.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="U18" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
         <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB18" t="n">
         <v>2.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>8.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.41</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.59</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE9" t="n">
         <v>1.13</v>
       </c>
       <c r="AF9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P10" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
         <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK10" t="n">
         <v>1.44</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,58 +2156,58 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>4.3</v>
+        <v>2.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.3</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
         <v>1.62</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.42</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>4.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.13</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>4.13</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,16 +2792,16 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
         <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
         <v>2.05</v>
@@ -2813,22 +2813,22 @@
         <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
         <v>2.25</v>
@@ -2837,7 +2837,7 @@
         <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="AD15" t="n">
         <v>1.18</v>
@@ -2865,7 +2865,7 @@
         <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.5</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.25</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.86</v>
+        <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>3.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U7" t="n">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.45</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.9</v>
-      </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="Q13" t="n">
         <v>2.4</v>
@@ -2489,10 +2489,10 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
         <v>3.3</v>
@@ -2504,7 +2504,7 @@
         <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
         <v>1.49</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.13</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
         <v>1.38</v>
@@ -2654,7 +2654,7 @@
         <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
         <v>1.33</v>
@@ -2663,10 +2663,10 @@
         <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
@@ -2675,22 +2675,22 @@
         <v>2.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,43 +2792,43 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q15" t="n">
         <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
         <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
         <v>2.25</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.19</v>
-      </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
         <v>2.09</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG16" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
         <v>2.09</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="P19" t="n">
         <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
         <v>1.95</v>
@@ -3446,16 +3446,16 @@
         <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
         <v>3.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
         <v>1.08</v>
@@ -3467,7 +3467,7 @@
         <v>2.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB19" t="n">
         <v>1.5</v>
@@ -3476,13 +3476,13 @@
         <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE19" t="n">
         <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AG19" t="n">
         <v>1.7</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -728,40 +728,40 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
         <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="n">
         <v>1.8</v>
@@ -776,13 +776,13 @@
         <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,61 +884,61 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
         <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
         <v>2.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
         <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
         <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
         <v>1.95</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.71</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -1064,22 +1064,22 @@
         <v>4.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
         <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.36</v>
@@ -1088,19 +1088,19 @@
         <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
         <v>1.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF4" t="n">
         <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
         <v>2.2</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.1</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.45</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AK6" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>2.5</v>
       </c>
       <c r="S8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.22</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>8.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
         <v>2.29</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AB9" t="n">
         <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
         <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
         <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="S10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.25</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="Q11" t="n">
         <v>2.45</v>
@@ -2186,7 +2186,7 @@
         <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.3</v>
@@ -2201,7 +2201,7 @@
         <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
         <v>1.25</v>
@@ -2210,7 +2210,7 @@
         <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
         <v>1.91</v>
@@ -2318,16 +2318,16 @@
         <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
         <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.61</v>
+        <v>5.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
         <v>1.33</v>
@@ -2336,7 +2336,7 @@
         <v>3.02</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
@@ -2345,13 +2345,13 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA12" t="n">
         <v>1.8</v>
@@ -2366,13 +2366,13 @@
         <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK12" t="n">
         <v>1.13</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.49</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
       </c>
       <c r="U13" t="n">
         <v>3.3</v>
@@ -2507,7 +2507,7 @@
         <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
         <v>2.5</v>
@@ -2525,7 +2525,7 @@
         <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
         <v>2.1</v>
@@ -2547,7 +2547,7 @@
         <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="R14" t="n">
         <v>2.1</v>
@@ -2669,28 +2669,28 @@
         <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA14" t="n">
         <v>2.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>4.19</v>
       </c>
       <c r="AD14" t="n">
         <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,22 +2792,22 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O15" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
         <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
         <v>2.54</v>
@@ -2825,10 +2825,10 @@
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
         <v>2.25</v>
@@ -2837,7 +2837,7 @@
         <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
         <v>1.18</v>
@@ -2846,10 +2846,10 @@
         <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.55</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.41</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA16" t="n">
         <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.19</v>
       </c>
       <c r="S17" t="n">
         <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="O19" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R19" t="n">
         <v>1.95</v>
@@ -3473,7 +3473,7 @@
         <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
         <v>1.12</v>
@@ -3485,7 +3485,7 @@
         <v>2.04</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
         <v>3.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T2" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
         <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.36</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S6" t="n">
         <v>1.25</v>
@@ -1382,31 +1382,31 @@
         <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
         <v>1.5</v>
@@ -1415,10 +1415,10 @@
         <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.25</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>7.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>2.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.5</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.09</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="n">
         <v>1.13</v>
       </c>
       <c r="AF10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.83</v>
+        <v>2.87</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.45</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.72</v>
+        <v>3.34</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.37</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>4.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.1</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,19 +2801,19 @@
         <v>3.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="V15" t="n">
         <v>1.31</v>
@@ -2837,35 +2837,35 @@
         <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
         <v>3.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="U2" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.36</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
         <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.83</v>
+        <v>2.87</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.45</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>3.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R11" t="n">
         <v>2.09</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="S11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.34</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.37</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>4.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.25</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.69</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>4.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.29</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.55</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.41</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="U18" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W18" t="n">
         <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
         <v>3.28</v>
@@ -3449,13 +3449,13 @@
         <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1.08</v>
@@ -3467,13 +3467,13 @@
         <v>2.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AB19" t="n">
         <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>6.62</v>
       </c>
       <c r="AD19" t="n">
         <v>1.12</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
         <v>3.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T2" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
         <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.36</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.09</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="S9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z9" t="n">
-        <v>4.35</v>
+        <v>3.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>7.5</v>
+        <v>2.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.18</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.69</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.1</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>7.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>3.18</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
         <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.86</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>3.83</v>
+        <v>7.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.04</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>3.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>4.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.25</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.69</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>4.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.29</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U18" t="n">
         <v>2.55</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.41</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
         <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.41</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
         <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.33</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.42</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>2.75</v>
@@ -1061,13 +1061,13 @@
         <v>1.17</v>
       </c>
       <c r="T4" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
@@ -1076,31 +1076,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.5</v>
+        <v>6.79</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG4" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,58 +1202,58 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
         <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF5" t="n">
         <v>1.57</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK5" t="n">
         <v>1.67</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.25</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.34</v>
+        <v>4.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.18</v>
+        <v>2.13</v>
       </c>
       <c r="R7" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.83</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK7" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1685,37 +1685,37 @@
         <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.41</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
         <v>1.66</v>
@@ -1724,16 +1724,16 @@
         <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
         <v>1.67</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
         <v>3.1</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.83</v>
+        <v>2.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.04</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.35</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,28 +2315,28 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V12" t="n">
         <v>1.45</v>
@@ -2345,7 +2345,7 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
         <v>1.25</v>
@@ -2354,22 +2354,22 @@
         <v>3.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
         <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
         <v>1.9</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.69</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.01</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>4.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.29</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>4.85</v>
       </c>
       <c r="Q15" t="n">
         <v>2.21</v>
@@ -2807,49 +2807,49 @@
         <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="V15" t="n">
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
         <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
         <v>1.28</v>
@@ -3131,10 +3131,10 @@
         <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
@@ -3143,31 +3143,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
         <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
         <v>1.44</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,25 +3431,25 @@
         <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="P19" t="n">
         <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S19" t="n">
         <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U19" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
@@ -3467,16 +3467,16 @@
         <v>2.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB19" t="n">
         <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.62</v>
+        <v>4.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
         <v>1.04</v>
@@ -3485,7 +3485,7 @@
         <v>2.04</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3596,55 +3596,55 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.25</v>
       </c>
-      <c r="P6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.88</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.28</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.25</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z10" t="n">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>4.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>2.13</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.69</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S13" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.19</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AK13" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.23</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.28</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
         <v>1.44</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.38</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P18" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.5</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.71</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AK3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>7.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.5</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.96</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.04</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z9" t="n">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
         <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
         <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>3.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.28</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="AD13" t="n">
         <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.19</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AK14" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.23</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="Q15" t="n">
         <v>2.21</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O19" t="n">
         <v>3.06</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q19" t="n">
         <v>3.3</v>
@@ -3449,7 +3449,7 @@
         <v>2.33</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
@@ -3501,7 +3501,7 @@
         <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.25</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z6" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>4.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.28</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="P8" t="n">
-        <v>7.75</v>
+        <v>4.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="R8" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>4.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.32</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S13" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.19</v>
+        <v>4.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.28</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>4.19</v>
       </c>
       <c r="AD14" t="n">
         <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q15" t="n">
         <v>2.21</v>
@@ -2807,16 +2807,16 @@
         <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
@@ -2825,16 +2825,16 @@
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
         <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
         <v>4.2</v>
@@ -2846,10 +2846,10 @@
         <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
         <v>1.44</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
         <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="R6" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
         <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
         <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
         <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>4.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="R11" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>3.32</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.28</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>4.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.19</v>
+        <v>4.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
         <v>1.44</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.38</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P18" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q2" t="n">
         <v>2.5</v>
@@ -746,7 +746,7 @@
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -758,19 +758,19 @@
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
         <v>3.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD2" t="n">
         <v>1.25</v>
@@ -782,7 +782,7 @@
         <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -887,22 +887,22 @@
         <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="R3" t="n">
         <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T3" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="U3" t="n">
         <v>2.5</v>
@@ -917,22 +917,22 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
         <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE3" t="n">
         <v>1.14</v>
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
         <v>3.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="R4" t="n">
         <v>2.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
         <v>1.83</v>
@@ -1073,31 +1073,31 @@
         <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.79</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
         <v>1.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG4" t="n">
         <v>2.8</v>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>2.45</v>
@@ -1232,7 +1232,7 @@
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.2</v>
@@ -1250,7 +1250,7 @@
         <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
         <v>1.15</v>
@@ -1367,22 +1367,22 @@
         <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S6" t="n">
         <v>1.34</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V6" t="n">
         <v>1.45</v>
@@ -1400,25 +1400,25 @@
         <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB6" t="n">
         <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
         <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
         <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
         <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="P8" t="n">
-        <v>7.75</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>1.73</v>
@@ -1709,13 +1709,13 @@
         <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA8" t="n">
         <v>1.66</v>
@@ -1730,10 +1730,10 @@
         <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
         <v>1.67</v>
@@ -1752,7 +1752,7 @@
         <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
         <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.91</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="S10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.38</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.55</v>
+        <v>2.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
         <v>2.38</v>
@@ -2177,43 +2177,43 @@
         <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,25 +2315,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
         <v>2.6</v>
@@ -2360,19 +2360,19 @@
         <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="AD12" t="n">
         <v>1.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" t="n">
         <v>1.14</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.32</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S13" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.19</v>
+        <v>4.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>4.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>5.2</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
         <v>2.21</v>
@@ -2807,7 +2807,7 @@
         <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T15" t="n">
         <v>2.59</v>
@@ -2819,10 +2819,10 @@
         <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.38</v>
@@ -2865,7 +2865,7 @@
         <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
         <v>2.3</v>
@@ -2972,13 +2972,13 @@
         <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
@@ -2990,10 +2990,10 @@
         <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC16" t="n">
         <v>2.5</v>
@@ -3002,7 +3002,7 @@
         <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
         <v>1.5</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3278,10 +3278,10 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S18" t="n">
         <v>1.28</v>
@@ -3308,13 +3308,13 @@
         <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
         <v>1.38</v>
@@ -3342,7 +3342,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
         <v>2.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
         <v>1.91</v>
@@ -3461,19 +3461,19 @@
         <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
         <v>1.16</v>
@@ -3602,43 +3602,43 @@
         <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T20" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
         <v>1.85</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.83</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.85</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>8.029999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>1.88</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>4.85</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="S11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
         <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.21</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.85</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.83</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.25</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.33</v>
+        <v>2.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.25</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.85</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>8.029999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="S9" t="n">
         <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.49</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.25</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.49</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R11" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>4.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U14" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.32</v>
+        <v>4.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>6.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>6.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -721,17 +721,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
         <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
         <v>2.5</v>
@@ -746,7 +746,7 @@
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -755,31 +755,31 @@
         <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
         <v>1.85</v>
@@ -791,41 +791,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
         <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46213.3125</v>
@@ -861,91 +861,91 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
         <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '41', '50', '59', '90+1']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46213.3125</v>
@@ -1020,130 +1020,130 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="R4" t="n">
         <v>2.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '16', '26', '54']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '76', '90+1']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46213.35763888889</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>8.029999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="S8" t="n">
         <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.49</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="P11" t="n">
-        <v>2.87</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.31</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>6.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
         <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>6.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
         <v>2.07</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S5" t="n">
         <v>1.3</v>
@@ -1223,16 +1223,16 @@
         <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
         <v>1.2</v>
@@ -1241,16 +1241,16 @@
         <v>4.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
         <v>1.15</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S6" t="n">
         <v>1.36</v>
@@ -1382,59 +1382,59 @@
         <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.88</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.5</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE7" t="n">
         <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
         <v>3.4</v>
@@ -1688,71 +1688,71 @@
         <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>5.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.87</v>
+        <v>9.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.38</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.31</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
         <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="U10" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>8.029999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,28 +2318,28 @@
         <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
         <v>1.07</v>
@@ -2351,7 +2351,7 @@
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
         <v>1.75</v>
@@ -2360,19 +2360,19 @@
         <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>4.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.32</v>
+        <v>4.6</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.95</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.01</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.67</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.15</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>2.37</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>6.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3272,16 +3272,16 @@
         <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.21</v>
       </c>
       <c r="S18" t="n">
         <v>1.28</v>
@@ -3296,7 +3296,7 @@
         <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
@@ -3308,7 +3308,7 @@
         <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
         <v>2.07</v>
@@ -3323,10 +3323,10 @@
         <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
         <v>3.25</v>
@@ -3446,13 +3446,13 @@
         <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
         <v>3.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
@@ -3461,13 +3461,13 @@
         <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
         <v>2.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB19" t="n">
         <v>1.48</v>
@@ -3476,13 +3476,13 @@
         <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>1.7</v>
@@ -3501,7 +3501,7 @@
         <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>1.43</v>
@@ -3623,13 +3623,13 @@
         <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>3.9</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1179,26 +1179,26 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '31', '90+3']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46213.54166666666</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>5.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>9.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
         <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>5.05</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>9.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.35</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P10" t="n">
         <v>3.4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.06</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.98</v>
+        <v>3.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>2.37</v>
+        <v>4.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
         <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
         <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -693,28 +693,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -725,77 +725,77 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.73</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>['12', '41', '50', '59', '90+1']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
         <v>1.83</v>
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="AS2" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46213.3125</v>
@@ -852,28 +852,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -884,77 +884,77 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['12', '41', '50', '59', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
         <v>1.83</v>
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AT3" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46213.3125</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,22 +1329,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1353,115 +1353,115 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>5.05</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>9.25</v>
+        <v>4.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>2.35</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
         <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['73', '85']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK6" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46213.65625</v>
@@ -1488,25 +1488,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1586,41 +1586,41 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46213.65625</v>
@@ -1647,39 +1647,39 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
         <v>3.4</v>
@@ -1688,98 +1688,98 @@
         <v>2.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>['8', '82']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46213.65625</v>
@@ -1806,139 +1806,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.06</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '90+4']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '86']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46213.65625</v>
@@ -1965,139 +1965,139 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>5.05</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>9.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['28', '70', '72']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>['11', '45+2', '86', '90+2']</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46213.65625</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="V11" t="n">
         <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>['18', '22', '46', '51', '77', '86']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46213.65625</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2307,11 +2307,11 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
@@ -2394,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46213.66666666666</v>
@@ -2654,7 +2654,7 @@
         <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="V14" t="n">
         <v>1.38</v>
@@ -2669,28 +2669,28 @@
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
         <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
       <c r="R19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>1.5</v>
@@ -3452,10 +3452,10 @@
         <v>3.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
         <v>1.08</v>
@@ -3467,13 +3467,13 @@
         <v>2.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AD19" t="n">
         <v>1.17</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK19" t="n">
         <v>1.38</v>

--- a/jogos_2026-07-10.xlsx
+++ b/jogos_2026-07-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,28 +1329,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.15</v>
+        <v>9.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
         <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['28', '70', '72']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['73', '85']</t>
+          <t>['11', '45+2', '86', '90+2']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="n">
         <v>14</v>
       </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AS6" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="AT6" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46213.65625</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,31 +1488,31 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.37</v>
+        <v>4.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['73', '85']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="AT7" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46213.65625</v>
@@ -1806,31 +1806,31 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,86 +1838,86 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.95</v>
       </c>
-      <c r="O9" t="n">
+      <c r="AC9" t="n">
         <v>3.1</v>
       </c>
-      <c r="P9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>['25', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>['30', '86']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN9" t="n">
         <v>6</v>
@@ -1926,19 +1926,19 @@
         <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AR9" t="n">
         <v>1.77</v>
       </c>
       <c r="AS9" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="AT9" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46213.65625</v>
@@ -1965,31 +1965,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5.05</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>9.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
         <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.38</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['28', '70', '72']</t>
+          <t>['18', '22', '46', '51', '77', '86']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['11', '45+2', '86', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.35</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AT10" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46213.65625</v>
@@ -2124,31 +2124,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P11" t="n">
         <v>3.4</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S11" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.49</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['18', '22', '46', '51', '77', '86']</t>
+          <t>['25', '90+4']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '86']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AS11" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="AT11" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46213.65625</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2470,111 +2470,111 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.95</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.6</v>
+        <v>4.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46213.79166666666</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2629,111 +2629,111 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>2.48</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="U14" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46213.79166666666</v>
@@ -2769,36 +2769,36 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="Q15" t="n">
         <v>2.38</v>
@@ -2807,31 +2807,31 @@
         <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T15" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
         <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB15" t="n">
         <v>1.57</v>
@@ -2849,50 +2849,50 @@
         <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '64', '90+6']</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '42', '76']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46213.83333333334</v>
@@ -2919,96 +2919,96 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
         <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3017,41 +3017,41 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '58']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46213.875</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3.33</v>
+        <v>3.91</v>
       </c>
       <c r="P17" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.39</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="P18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB18" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.64</v>
+        <v>5.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46213.875</v>
+        <v>46213.88541666666</v>
       </c>
     </row>
     <row r="19">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="U19" t="n">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46213.88541666666</v>
+        <v>46213.91875</v>
       </c>
     </row>
     <row r="20">
@@ -3587,52 +3587,52 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
         <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
         <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
         <v>1.2</v>
@@ -3641,10 +3641,10 @@
         <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
